--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES I-X/FRACC I/LTAIPT_A63F01.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES I-X/FRACC I/LTAIPT_A63F01.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_341DB85961F4FD8C807036C29C623E91FB003F97" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{2D9D715B-DE3D-4355-BFC0-757339DBCDB2}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="7365"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -18,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="255">
   <si>
     <t>48946</t>
   </si>
@@ -134,418 +140,598 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2021</t>
+    <t>5F06F623639C63E2A3342AFFB846DE07</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>Ley Federal</t>
+  </si>
+  <si>
+    <t>Código de Procedimientos Civiles vigente en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/11/1980</t>
+  </si>
+  <si>
+    <t>04/09/2018</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_de_proced_civiles040918.pdf</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>27/12/2023</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>8EFC7E98C1E72CF5B4BB4408F27080F2</t>
+  </si>
+  <si>
+    <t>3CAF31D7B211CCE95A5ADA3DB043420D</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>Constitución Política de los Estados Unidos Mexicanos</t>
+  </si>
+  <si>
+    <t>05/02/2017</t>
+  </si>
+  <si>
+    <t>28/05/2021</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/CPEUM.pdf</t>
+  </si>
+  <si>
+    <t>7CEFB98E7F72AAB97CDE06C2B6CC88B1</t>
+  </si>
+  <si>
+    <t>Tratado internacional</t>
+  </si>
+  <si>
+    <t>Convención Americana sobre los Derechos del Hombre (Pacto de San José)</t>
+  </si>
+  <si>
+    <t>18/07/1978</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CONVENCIONAAMERICANA%20SOBRED.H..pdf</t>
+  </si>
+  <si>
+    <t>9F134A6795B67B3BB64242DD6E236704</t>
+  </si>
+  <si>
+    <t>Pacto internacional de Derechos Civiles y Politicos</t>
+  </si>
+  <si>
+    <t>20/05/1981</t>
+  </si>
+  <si>
+    <t>22/06/1981</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Juridica/PACTO%20INTERNACIONAL%20DE%20DERECHOS%20CIVILES%20Y%20POLITICOS.pdf</t>
+  </si>
+  <si>
+    <t>Subdireccion Juridica</t>
+  </si>
+  <si>
+    <t>83A83C87B9206853723468B18F852769</t>
+  </si>
+  <si>
+    <t>Pacto Internacional de Derechos Economicos Sociales y Culturales</t>
+  </si>
+  <si>
+    <t>03/01/1973</t>
+  </si>
+  <si>
+    <t>03/01/1971</t>
+  </si>
+  <si>
+    <t>https://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Juridica/PACTO%20INTERNACIONAL%20DE%20DERECHOS%20ECONOMICOS%20SOCIALES%20Y%20CULTURALES.pdf</t>
+  </si>
+  <si>
+    <t>1A7B76301B84EA9A73C9BF87A518CD95</t>
+  </si>
+  <si>
+    <t>Convención sobre los Derechos del Niño</t>
+  </si>
+  <si>
+    <t>09/06/1994</t>
+  </si>
+  <si>
+    <t>20/11/1989</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Convenci%c3%b3nsobrederechosdelni%c3%b1o.pdf</t>
+  </si>
+  <si>
+    <t>1175879649BFE9D013095EA316867B1E</t>
+  </si>
+  <si>
+    <t>Convención Interamericana para Prevenir, Sancionar y Erradicar la Violencia contra la Mujer (Convención de Belém Do Pará)</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CONVENCION%20PARA%20prevenir,sancionar%20y%20erradicar%20violenciamujer.pdf</t>
+  </si>
+  <si>
+    <t>147B32BBBD56EEC450621163310B5077</t>
+  </si>
+  <si>
+    <t>Co85-Convenio sobre la Inspección del Trabajo, 1947 (núm. 85)</t>
+  </si>
+  <si>
+    <t>11/07/1947</t>
+  </si>
+  <si>
+    <t>https://www.ilo.org/dyn/normlex/es/f?p=NORMLEXPUB:12100:0::NO::P12100_ILO_CODE:C085</t>
+  </si>
+  <si>
+    <t>B70C7773F3C7FCD8D077E0EB9B55C92B</t>
+  </si>
+  <si>
+    <t>Co-87- Convenio Sobre la Libertad Sindical y la Protección del Derecho de Sindicación, 1948 (núm. 87)</t>
+  </si>
+  <si>
+    <t>09/07/1948</t>
+  </si>
+  <si>
+    <t>https://www.ilo.org/dyn/normlex/es/f?p=NORMLEXPUB:12100:0::NO::P12100_ILO_CODE:C087</t>
+  </si>
+  <si>
+    <t>DB24CAD6CD39BB2CAF54F03052795B69</t>
+  </si>
+  <si>
+    <t>Constitución Política de la entidad federativa</t>
+  </si>
+  <si>
+    <t>Constitución Politica del Estado Libre y Soberano de Tlaxcala</t>
+  </si>
+  <si>
+    <t>25/04/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Constitucion_Pol-Tlaxcala250422pdf.pdf</t>
+  </si>
+  <si>
+    <t>A3A35E35028B55DD921DFE2794046549</t>
+  </si>
+  <si>
+    <t>Ley General</t>
+  </si>
+  <si>
+    <t>Ley General de Educación</t>
+  </si>
+  <si>
+    <t>30/09/2019</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Nueva%20Ley%20General%20de%20Educaci%C3%B3n.pdf</t>
+  </si>
+  <si>
+    <t>96802BE3ED6BD4C4F4FC32834F5025BA</t>
+  </si>
+  <si>
+    <t>Ley General para la Carrera de las Maestras y los Maestros</t>
+  </si>
+  <si>
+    <t>30/03/2019</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Gral%20del%20Sistema%20para%20la%20carrera%20de%20las%20maestras%20y%20maestros.pdf</t>
+  </si>
+  <si>
+    <t>5D14AB5EB153A05A494B3E1CEF147F22</t>
+  </si>
+  <si>
+    <t>Ley Federal del Trabajo</t>
+  </si>
+  <si>
+    <t>01/05/1970</t>
+  </si>
+  <si>
+    <t>18/05/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/LeyFederalTrabajo180522.pdf</t>
+  </si>
+  <si>
+    <t>AFE9B1E4FA62BBB8628A07429BE76FCB</t>
+  </si>
+  <si>
+    <t>Ley Orgánica</t>
+  </si>
+  <si>
+    <t>Ley Orgánica para la Administración Pública del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>07/04/1948</t>
+  </si>
+  <si>
+    <t>02/06/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/reglamento%20interior%20de%20la%20secretaria%20de%20la%20funcion%20publica%20tlax%20220212.pdf</t>
+  </si>
+  <si>
+    <t>CE8E45DC14A0AB0081EBA85986953B1F</t>
+  </si>
+  <si>
+    <t>Ley Local</t>
+  </si>
+  <si>
+    <t>Ley de Educación para el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>29/11/2000</t>
+  </si>
+  <si>
+    <t>31/03/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_educacion_Tlax310322.pdf</t>
+  </si>
+  <si>
+    <t>8139E1134B35D2AB43567EF1CBCA3E85</t>
+  </si>
+  <si>
+    <t>Ley Laboral de los Servidores Públicos del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>31/12/2017</t>
+  </si>
+  <si>
+    <t>22/12/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_laboral_Serv_Pub_Tlax_y_Mpios221221.pdf</t>
+  </si>
+  <si>
+    <t>80F1B7E9A8E3C5AC67FC396999B20649</t>
+  </si>
+  <si>
+    <t>Ley de las Entidades Paraestatales del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/10/1995</t>
+  </si>
+  <si>
+    <t>12/04/2018</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_las_entidades_paraestatales_tlax120418.pdf</t>
+  </si>
+  <si>
+    <t>D75DEBC18C8F24928F1C15AC084C4B6D</t>
+  </si>
+  <si>
+    <t>Ley del Procedimiento Administrativo del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>30/11/2001</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_del_procedimiento_Admtvo_Tlax120418.pdf</t>
+  </si>
+  <si>
+    <t>F25DC7618D7C2D6B9BB9076B7DBCC93D</t>
+  </si>
+  <si>
+    <t>Ley de Entrega- Recepción para el Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>18/05/2011</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Entrega_Recepcion_para_el_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
+  </si>
+  <si>
+    <t>C979E7E56CE38E311740724F1AD1B35D</t>
+  </si>
+  <si>
+    <t>Ley de Protección de Datos Personales en Posesión de Sujetos Obligados del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>14/05/2012</t>
+  </si>
+  <si>
+    <t>18/07/2017</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/LEY_DE_DATOS.pdf</t>
+  </si>
+  <si>
+    <t>92A7D6A9E22481DA6D5DE302F0000389</t>
+  </si>
+  <si>
+    <t>Ley de Archivos del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>13/05/2011</t>
+  </si>
+  <si>
+    <t>10/05/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_Archivos_Tlaxcala100521.pdf</t>
+  </si>
+  <si>
+    <t>C08AA9F3799B78A08429251F36A3A7CC</t>
+  </si>
+  <si>
+    <t>Ley de Mejora Regulatoria del Estado de Tlaxcala y sus Municipios</t>
+  </si>
+  <si>
+    <t>09/05/2013</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Mejora_Regulatoria_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
+  </si>
+  <si>
+    <t>135DF79C596211DF11DD84CC79066F19</t>
+  </si>
+  <si>
+    <t>Ley de Transparencia y Acceso a la Información Pública del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>22/05/2012</t>
+  </si>
+  <si>
+    <t>13/09/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/Ley_de_transparencia-Tlax_aaceso_inf_pub_tlax1430921.pdf</t>
+  </si>
+  <si>
+    <t>74644C92FF173F6AAD6D9B99A760D24D</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>05/08/1981</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_que_crea_el_Colegio_de_Bachilleres_del_Estado_de_Tlaxcala.pdf</t>
+  </si>
+  <si>
+    <t>7838A6C284C4A6972E1D94D3BD1D9387</t>
+  </si>
+  <si>
+    <t>Ley Reglamentaria del Artículo 3ro de la Constitución Política de los Estados Unidos Mexicanos, en Materia de Mejora Continua de la Educación</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Reglamentaria%20del%20art.%203%20de%20la%20CPM%20en%20materia%20de%20mejora%20continua%20de%20la%20Educacion.pdf</t>
+  </si>
+  <si>
+    <t>8B2F9C70EE6D3626C9AC18355A88D81C</t>
+  </si>
+  <si>
+    <t>Código Civil en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>20/11/1976</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_civil_Tlax240422.pdf</t>
+  </si>
+  <si>
+    <t>22DFC9A8F34B108114DB03E82B3CA1E9</t>
+  </si>
+  <si>
+    <t>Código Penal Federal</t>
+  </si>
+  <si>
+    <t>14/08/2031</t>
+  </si>
+  <si>
+    <t>12/11/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CODIGO-PENAL-FED121121.pdf</t>
+  </si>
+  <si>
+    <t>1E7D0A8CEB815CFEF5C821401B2B5783</t>
+  </si>
+  <si>
+    <t>Código Nacional de Procedimientos Penales</t>
+  </si>
+  <si>
+    <t>05/03/2014</t>
+  </si>
+  <si>
+    <t>09/02/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/CODIGO-NAC-PROCED-PENALES_190221.pdf</t>
+  </si>
+  <si>
+    <t>BFB2A8998C00E6660996510BD903A44D</t>
+  </si>
+  <si>
+    <t>Código Penal vigente en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>02/01/1980</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/codigo_penal_TLAX130921.pdf</t>
+  </si>
+  <si>
+    <t>3215DD59D2C0C5CA12EA46C5203C11A7</t>
+  </si>
+  <si>
+    <t>Código de Conducta para las y los Servidores Públicos del Organismo Público Desconcentrado del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>28/04/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/CODIGO%20DE%20CONDUCTA%20COBAT.pdf</t>
+  </si>
+  <si>
+    <t>1AE639EF140D78DEF1B347A3A677E6F1</t>
+  </si>
+  <si>
+    <t>Código de Ética y Reglas de Integridad para las y los Servidores Públicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>07/07/2021</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202022/Subdireccion%20Juridica/1er_Trimestre/C%C3%93DIGO%20DE%20%C3%89TICA%20Y%20REGLAS%20DE%20INTEGRIDAD%20DE%20COBAT%20PUBLICADO%20EN%20PERI%C3%93DICO%20OFICIAL.pdf</t>
+  </si>
+  <si>
+    <t>8ABCA472FB03FCCF3512331BF2E38F9A</t>
+  </si>
+  <si>
+    <t>Reglamento General de la Ley que Crea al Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>06/02/1985</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Juridica/2do_Trimestre/PUBLICACI%c3%93N%20PER.%20OFICIAL%20REGLAMENTO%20INTERIOR%20COBAT.pdf</t>
+  </si>
+  <si>
+    <t>6798C6B5D8E2352E612CAE04CA7D4BF8</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>4944BC395BB0EEC504E3539146E75D0B</t>
+  </si>
+  <si>
+    <t>Reglamento Interior de la Secretaría de la Función Pública</t>
+  </si>
+  <si>
+    <t>22/02/2012</t>
+  </si>
+  <si>
+    <t>0601D7D2175664AA0D0D2AC62F9CC225</t>
+  </si>
+  <si>
+    <t>8C07D197DDD02882AF45CD80EAD253C1</t>
+  </si>
+  <si>
+    <t>9A15470A1F50E153116154C4AE2BE58B</t>
+  </si>
+  <si>
+    <t>9F4435FA0495BEB394900259668E5216</t>
+  </si>
+  <si>
+    <t>ECC4E124C7B43D1A3A2A0950DA028029</t>
+  </si>
+  <si>
+    <t>DC4870698DED7B48E72447B83EE47A8C</t>
+  </si>
+  <si>
+    <t>2ACCF2628B78EB0C2068B24D4F9717EF</t>
+  </si>
+  <si>
+    <t>9388DDFFF956947523115448BCCCCA32</t>
+  </si>
+  <si>
+    <t>5D9D0A2320DA263CFF0C199A59DF3FE6</t>
+  </si>
+  <si>
+    <t>64DD34A6D5132C216E0DDBC7FCDB7BAF</t>
+  </si>
+  <si>
+    <t>6B9C01E115AD4F6F245AB5C839EF20EF</t>
+  </si>
+  <si>
+    <t>629CC74F9F41CF835BAEF4EF8B123636</t>
+  </si>
+  <si>
+    <t>13282C682E836637A156973A78814978</t>
+  </si>
+  <si>
+    <t>88C9399940FE26EAFB299B2A7AB9F88E</t>
+  </si>
+  <si>
+    <t>059AAAE33EEC4381D121344C4261446B</t>
+  </si>
+  <si>
+    <t>E123214A35EF39E04C10C5FB546A5E41</t>
+  </si>
+  <si>
+    <t>FBD92CBC1A90B64465214A8E6E0C42B2</t>
+  </si>
+  <si>
+    <t>9608A5AE7ED475CC6C2C4844C70B6A31</t>
+  </si>
+  <si>
+    <t>6273BE2F6B9888F49E9CE8ED0799DB0F</t>
+  </si>
+  <si>
+    <t>830F023FE97F335720F3DE585002B008</t>
+  </si>
+  <si>
+    <t>5864F4F28D35EBCF011D4F6428281DD5</t>
+  </si>
+  <si>
+    <t>D1BC124E4D2988564A67E5ED05DF6669</t>
+  </si>
+  <si>
+    <t>603A74C37D3A8C985CBDC33AD9B1C3E7</t>
+  </si>
+  <si>
+    <t>06CB6D1183665B95E3C9B9B8D466ABDB</t>
+  </si>
+  <si>
+    <t>606F70A110144932F0FDF8D62ADBB264</t>
+  </si>
+  <si>
+    <t>24040D4F31F95A83543A18875B4463D6</t>
+  </si>
+  <si>
+    <t>3BA8ED2C186BA2F0AC32924D1039E9FB</t>
+  </si>
+  <si>
+    <t>C97DDBF9F64B1B4E30C44EB2A85C96D9</t>
+  </si>
+  <si>
+    <t>3A185BD6824C6B48CF32A41B81438202</t>
+  </si>
+  <si>
+    <t>C73B1852E2B41602E6C0A0567101BA3B</t>
+  </si>
+  <si>
+    <t>7F8B16BDCC90C1287F84F586A3CA73F8</t>
+  </si>
+  <si>
+    <t>791EDCC03D4B59EAD1AEE009B9DB8BEC</t>
+  </si>
+  <si>
+    <t>FCE3FC55FEB1E90471E11499D62325D9</t>
+  </si>
+  <si>
+    <t>Estatuto</t>
+  </si>
+  <si>
+    <t>Ley Reglamentaria</t>
   </si>
   <si>
     <t>Código</t>
   </si>
   <si>
-    <t>Código Civil vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>20/11/1976</t>
-  </si>
-  <si>
-    <t>30/12/2016</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/C%C3%B3digo-Civil-para-el-Estado-Libre-y-Soberano-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Código de Procedimientos Civiles vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/11/1980</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/C%C3%B3digo-de-Procedimientos-Civiles-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Código Penal Penal Federal</t>
-  </si>
-  <si>
-    <t>14/08/2031</t>
-  </si>
-  <si>
-    <t>24/01/2020</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202020/Subdireccion%20Juridica/1er-Trimestre/Codigo_Penal_Federal_Reforma240120.pdf</t>
-  </si>
-  <si>
-    <t>Código Nacional de Procedimientos Penales</t>
-  </si>
-  <si>
-    <t>05/03/2014</t>
-  </si>
-  <si>
-    <t>22/01/2020</t>
-  </si>
-  <si>
-    <t>Código Penal vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>02/01/1980</t>
-  </si>
-  <si>
-    <t>19/05/2016</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/C%C3%B3digo-Penal-para-el-Estado-Libre-y-Soberano-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Código de Procedimientos Penales vigente en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>18/12/1979</t>
-  </si>
-  <si>
-    <t>24/12/2014</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/C%C3%B3digo-de-Procedimientos-Penales-para-el-Estado-Libre-y-Soberano-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
     <t>Reglamento</t>
-  </si>
-  <si>
-    <t>Reglamento Interior de la Contraloria del Ejecutivo del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>16/10/2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Reglamento%20Interior%20de%20la%20Contralor%C3%ADa%20del%20Ejecutivo%20del%20Estado%20de%20Tlaxcala%2016oct2019.pdf</t>
-  </si>
-  <si>
-    <t>Al ser un nuevo Reglamento  no existe fecha de modificación o reforma</t>
-  </si>
-  <si>
-    <t>Estatuto</t>
-  </si>
-  <si>
-    <t>Manual de Organizaciòn para los Servidores Pùblicos del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Documento admnistrativo interno en revisiòn ante la Contraloria del Ejecutivo para su validaciòn y autorizaciòn</t>
-  </si>
-  <si>
-    <t>Manual de Procedimientos de Control Interno del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Constitución Política de los Estados Unidos Mexicanos</t>
-  </si>
-  <si>
-    <t>05/02/2017</t>
-  </si>
-  <si>
-    <t>28/05/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20Juridica/2do_Trimestre/Facultades_de_cada_area/Const.%20Fedral%2028-mayo-21.pdf</t>
-  </si>
-  <si>
-    <t>Constitución Política de la entidad federativa</t>
-  </si>
-  <si>
-    <t>Constitución Política del Estado Libre y Soberano de Tlaxcala</t>
-  </si>
-  <si>
-    <t>18/07/2017</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/CONSTITUCION-LOCAL.pdf</t>
-  </si>
-  <si>
-    <t>Ley General</t>
-  </si>
-  <si>
-    <t>Ley General de Educación</t>
-  </si>
-  <si>
-    <t>30/09/2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Nueva%20Ley%20General%20de%20Educaci%C3%B3n.pdf</t>
-  </si>
-  <si>
-    <t>Al ser una Ley de nueva creación, no existe fecha de modificación o reforma</t>
-  </si>
-  <si>
-    <t>Ley Reglamentaria</t>
-  </si>
-  <si>
-    <t>Ley Reglamentaria del Artículo 3o. de la Constitución Política de los Estados Unidos Mexicanos,  en materia de Mejora Continua de la Educación</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Reglamentaria%20del%20art.%203%20de%20la%20CPM%20en%20materia%20de%20mejora%20continua%20de%20la%20Educacion.pdf</t>
-  </si>
-  <si>
-    <t>Ley General del Sistema para la Carrera de las Maestras y los Maestros</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/Ley%20general%20de%20Educacion%202019/Ley%20Gral%20del%20Sistema%20para%20la%20carrera%20de%20las%20maestras%20y%20maestros.pdf</t>
-  </si>
-  <si>
-    <t>Ley Local</t>
-  </si>
-  <si>
-    <t>Ley de Educación para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>29/11/2000</t>
-  </si>
-  <si>
-    <t>17/08/2017</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Educacion_para_el_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley Federal</t>
-  </si>
-  <si>
-    <t>Ley Federal del Trabajo</t>
-  </si>
-  <si>
-    <t>01/05/1970</t>
-  </si>
-  <si>
-    <t>02/07/2019</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/ley%20federal%20del%20Trab.pdf</t>
-  </si>
-  <si>
-    <t>Ley Laboral de los Servidores Públicos del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>31/12/2007</t>
-  </si>
-  <si>
-    <t>12/12/2013</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_Laboral_de_los_Servidores_Publicos_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley Orgánica</t>
-  </si>
-  <si>
-    <t>Ley Orgánica de la Administración Pública del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>07/04/1998</t>
-  </si>
-  <si>
-    <t>30/12/2015</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_Organica_de_la_Administracion_Publica_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley de las Entidades Paraestatales para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/10/1995</t>
-  </si>
-  <si>
-    <t>17/10/2008</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_las_Entidades_Paraestatales_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley del Procedimiento Administrativo del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>30/11/2001</t>
-  </si>
-  <si>
-    <t>30/11/2011</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_del_Procedimiento_Administrativo_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Transparencia y Acceso a la Información Pública para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>22/05/2012</t>
-  </si>
-  <si>
-    <t>15/11/2016</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Transparencia_y_Acceso_a_la_Informacion_Publica_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Entrega-Recepción para el Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>18/05/2011</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Entrega_Recepcion_para_el_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Protección de Datos Personales para el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>14/05/2012</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/LEY_DE_DATOS.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Archivos del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>13/05/2011</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Archivos_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Ley de Mejora Regulatoria del Estado de Tlaxcala y sus Municipios</t>
-  </si>
-  <si>
-    <t>09/05/2013</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_de_Mejora_Regulatoria_del_Estado_de_Tlaxcala_y_sus_Municipios.pdf</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>05/08/1981</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Ley_que_crea_el_Colegio_de_Bachilleres_del_Estado_de_Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Reglamento General de la Ley que Crea El Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>06/02/1985</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202019/Subdireccion%20Juridica/leyes%20y%20reglamentos/Reglamento-General-de-la-Ley-Que-Crea-el-Colegio-de-Bachilleres-del-Estado-de-Tlaxcala.pdf</t>
-  </si>
-  <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>28/04/2021</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/portal/pdf.html?p=transparencia/RICOBAT&amp;t=REGLAMENTO%20INTERIOR%20COBAT</t>
-  </si>
-  <si>
-    <t>F23D42B5A0049988</t>
-  </si>
-  <si>
-    <t>01/10/2021</t>
-  </si>
-  <si>
-    <t>31/12/2021</t>
-  </si>
-  <si>
-    <t>17/12/2021</t>
-  </si>
-  <si>
-    <t>6F9375B8A005DB5A</t>
-  </si>
-  <si>
-    <t>D33A7C2E8BDD3764</t>
-  </si>
-  <si>
-    <t>645AE057C6B09E15</t>
-  </si>
-  <si>
-    <t>11C969F450D5F06B</t>
-  </si>
-  <si>
-    <t>3C3E00B8FBE1DA85</t>
-  </si>
-  <si>
-    <t>7CF491179C2FCCB4</t>
-  </si>
-  <si>
-    <t>0F3311FD5F7F361F</t>
-  </si>
-  <si>
-    <t>4E89C46859D02C26</t>
-  </si>
-  <si>
-    <t>1716B07878A01E90</t>
-  </si>
-  <si>
-    <t>41A21DB2FCA74428</t>
-  </si>
-  <si>
-    <t>80D90C296FCE363B</t>
-  </si>
-  <si>
-    <t>3246ACC6A313E158</t>
-  </si>
-  <si>
-    <t>9BE72453CA9B8BED</t>
-  </si>
-  <si>
-    <t>A53715FC98149BB0</t>
-  </si>
-  <si>
-    <t>5551CE67C14A2E02</t>
-  </si>
-  <si>
-    <t>A6D6AADE09127019</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de octubre de 2021 al 31 de diciembre de 2021, el Colegio de Bachilleres del Estado de Tlaxcala, hace una versión pública de esta Ley, la cual durante este periodo no ha tenido ninguna reforma</t>
-  </si>
-  <si>
-    <t>D9A02C9DDFDA490A</t>
-  </si>
-  <si>
-    <t>68E7DF86830DADCE</t>
-  </si>
-  <si>
-    <t>50AA6C6E0CA9C39F</t>
-  </si>
-  <si>
-    <t>C7974B7EF5822E81</t>
-  </si>
-  <si>
-    <t>012436521202181F</t>
-  </si>
-  <si>
-    <t>58F1715E7D79B54C</t>
-  </si>
-  <si>
-    <t>0517B32D9AFFCA67</t>
-  </si>
-  <si>
-    <t>61F88150BCC1D00C</t>
-  </si>
-  <si>
-    <t>C2B014D8BAE8C69F</t>
-  </si>
-  <si>
-    <t>9FC5CC193366F585</t>
-  </si>
-  <si>
-    <t>3EB920165EB0313A</t>
-  </si>
-  <si>
-    <t>Tratado internacional</t>
   </si>
   <si>
     <t>Decreto</t>
@@ -608,7 +794,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -679,7 +865,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -694,9 +880,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -706,6 +889,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -722,44 +908,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -787,14 +973,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -822,6 +1025,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -833,187 +1053,163 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="121.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="121" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="242.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="179.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -1186,1150 +1382,2790 @@
     </row>
     <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G8" s="6">
-        <v>42771</v>
+        <v>43</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M8" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M9" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>158</v>
+        <v>99</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>58</v>
+        <v>155</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>61</v>
+        <v>159</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="G36" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K35" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>71</v>
+      <c r="I63" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2343,7 +4179,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E145">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -2352,158 +4188,158 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>194</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
